--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_individual_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_individual_h_11.xlsx
@@ -658,7 +658,7 @@
         <v>0.008520536396819937</v>
       </c>
       <c r="C2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>48067128</v>
+        <v>3973575</v>
       </c>
       <c r="L2" t="n">
-        <v>25395755</v>
+        <v>1700445</v>
       </c>
       <c r="M2" t="n">
-        <v>5861341</v>
+        <v>301556</v>
       </c>
       <c r="N2" t="n">
-        <v>285301</v>
+        <v>6584</v>
       </c>
       <c r="O2" t="n">
-        <v>3451754</v>
+        <v>184752</v>
       </c>
       <c r="P2" t="n">
-        <v>1281825</v>
+        <v>448</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999858736991882</v>
+        <v>0.9999949336051941</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8348003029823303</v>
+        <v>0.7212334275245667</v>
       </c>
       <c r="S2" t="n">
-        <v>0.703269898891449</v>
+        <v>0.5308442711830139</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6373264789581299</v>
+        <v>0.4035938084125519</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2359085828065872</v>
+        <v>0.04461399838328362</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6797961592674255</v>
+        <v>0.4007331430912018</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8057181239128113</v>
+        <v>0.4076433181762695</v>
       </c>
       <c r="X2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>53079081</v>
+        <v>4775969</v>
       </c>
       <c r="AG2" t="n">
-        <v>33018842</v>
+        <v>3037162</v>
       </c>
       <c r="AH2" t="n">
-        <v>8835934</v>
+        <v>808667</v>
       </c>
       <c r="AI2" t="n">
-        <v>651291</v>
+        <v>59431</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5060281</v>
+        <v>461766</v>
       </c>
       <c r="AK2" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9559435248374939</v>
+        <v>0.9546229243278503</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116207361221313</v>
+        <v>0.912503182888031</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580287098884583</v>
+        <v>0.8579802513122559</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6615698337554932</v>
+        <v>0.6605058908462524</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.901967465877533</v>
+        <v>0.9019959568977356</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314546585083008</v>
+        <v>0.9314878582954407</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002039522590464157</v>
       </c>
       <c r="C3" t="n">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>48067128</v>
+        <v>3973575</v>
       </c>
       <c r="E3" t="n">
-        <v>7119850</v>
+        <v>965306</v>
       </c>
       <c r="F3" t="n">
-        <v>210892</v>
+        <v>41537</v>
       </c>
       <c r="G3" t="n">
-        <v>21655</v>
+        <v>4301</v>
       </c>
       <c r="H3" t="n">
-        <v>14188</v>
+        <v>3952</v>
       </c>
       <c r="I3" t="n">
-        <v>789</v>
+        <v>36</v>
       </c>
       <c r="J3" t="n">
-        <v>110764834</v>
+        <v>10069588</v>
       </c>
       <c r="K3" t="n">
-        <v>115629359</v>
+        <v>9891445</v>
       </c>
       <c r="L3" t="n">
-        <v>133567563</v>
+        <v>11573255</v>
       </c>
       <c r="M3" t="n">
-        <v>166930719</v>
+        <v>15025996</v>
       </c>
       <c r="N3" t="n">
-        <v>178666475</v>
+        <v>16184900</v>
       </c>
       <c r="O3" t="n">
-        <v>173335964</v>
+        <v>15627139</v>
       </c>
       <c r="P3" t="n">
-        <v>178138370</v>
+        <v>16221417</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.867096483707428</v>
+        <v>0.7965129017829895</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6997381448745728</v>
+        <v>0.5091295838356018</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5685181021690369</v>
+        <v>0.3193153738975525</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2895119488239288</v>
+        <v>0.07306868582963943</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6148301362991333</v>
+        <v>0.3604368567466736</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6022071242332458</v>
+        <v>0.002310088137164712</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>53079081</v>
+        <v>4775969</v>
       </c>
       <c r="Z3" t="n">
-        <v>2185497</v>
+        <v>197364</v>
       </c>
       <c r="AA3" t="n">
-        <v>93996</v>
+        <v>8471</v>
       </c>
       <c r="AB3" t="n">
-        <v>75314</v>
+        <v>6869</v>
       </c>
       <c r="AC3" t="n">
-        <v>359</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>330</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>110765820</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>122695174</v>
+        <v>11200265</v>
       </c>
       <c r="AG3" t="n">
-        <v>141081682</v>
+        <v>12784871</v>
       </c>
       <c r="AH3" t="n">
-        <v>168804129</v>
+        <v>15337760</v>
       </c>
       <c r="AI3" t="n">
-        <v>179257373</v>
+        <v>16295346</v>
       </c>
       <c r="AJ3" t="n">
-        <v>174411852</v>
+        <v>15853250</v>
       </c>
       <c r="AK3" t="n">
-        <v>178301599</v>
+        <v>16208790</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575085639953613</v>
+        <v>0.957354724407196</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097797274589539</v>
+        <v>0.9093555212020874</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8570374250411987</v>
+        <v>0.8562913537025452</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6609038710594177</v>
+        <v>0.6595603227615356</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013426303863525</v>
+        <v>0.9008697271347046</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311618804931641</v>
+        <v>0.9308778047561646</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03216441684267991</v>
       </c>
       <c r="C4" t="n">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>8780239</v>
+        <v>1372088</v>
       </c>
       <c r="E4" t="n">
-        <v>25395755</v>
+        <v>1700445</v>
       </c>
       <c r="F4" t="n">
-        <v>1771175</v>
+        <v>207011</v>
       </c>
       <c r="G4" t="n">
-        <v>130813</v>
+        <v>23351</v>
       </c>
       <c r="H4" t="n">
-        <v>197915</v>
+        <v>36857</v>
       </c>
       <c r="I4" t="n">
-        <v>17258</v>
+        <v>142</v>
       </c>
       <c r="J4" t="n">
-        <v>986</v>
+        <v>32</v>
       </c>
       <c r="K4" t="n">
-        <v>9512064</v>
+        <v>1535841</v>
       </c>
       <c r="L4" t="n">
-        <v>10715211</v>
+        <v>1502839</v>
       </c>
       <c r="M4" t="n">
-        <v>3335423</v>
+        <v>445621</v>
       </c>
       <c r="N4" t="n">
-        <v>924070</v>
+        <v>140993</v>
       </c>
       <c r="O4" t="n">
-        <v>1625877</v>
+        <v>276283</v>
       </c>
       <c r="P4" t="n">
-        <v>309085</v>
+        <v>651</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999929070472717</v>
+        <v>0.9999974370002747</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8506419658660889</v>
+        <v>0.7570062279701233</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7014995813369751</v>
+        <v>0.5197602510452271</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6009590625762939</v>
+        <v>0.3565418720245361</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2599759697914124</v>
+        <v>0.05540129169821739</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6456831097602844</v>
+        <v>0.3795183598995209</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6892542243003845</v>
+        <v>0.004594141617417336</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2284621</v>
+        <v>212190</v>
       </c>
       <c r="Z4" t="n">
-        <v>33018842</v>
+        <v>3037162</v>
       </c>
       <c r="AA4" t="n">
-        <v>915390</v>
+        <v>83722</v>
       </c>
       <c r="AB4" t="n">
-        <v>61077</v>
+        <v>5633</v>
       </c>
       <c r="AC4" t="n">
-        <v>12548</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>748</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2446249</v>
+        <v>227021</v>
       </c>
       <c r="AG4" t="n">
-        <v>3201092</v>
+        <v>291223</v>
       </c>
       <c r="AH4" t="n">
-        <v>1462013</v>
+        <v>133857</v>
       </c>
       <c r="AI4" t="n">
-        <v>333172</v>
+        <v>30547</v>
       </c>
       <c r="AJ4" t="n">
-        <v>549989</v>
+        <v>50172</v>
       </c>
       <c r="AK4" t="n">
-        <v>145856</v>
+        <v>13278</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567253589630127</v>
+        <v>0.9559868574142456</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106993675231934</v>
+        <v>0.9109266996383667</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8575327396392822</v>
+        <v>0.857134997844696</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6612366437911987</v>
+        <v>0.6600327491760254</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016548991203308</v>
+        <v>0.9014324545860291</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313082695007324</v>
+        <v>0.9311826825141907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>129</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>525072</v>
+        <v>121629</v>
       </c>
       <c r="E5" t="n">
-        <v>2903240</v>
+        <v>399774</v>
       </c>
       <c r="F5" t="n">
-        <v>5861341</v>
+        <v>301556</v>
       </c>
       <c r="G5" t="n">
-        <v>287159</v>
+        <v>37765</v>
       </c>
       <c r="H5" t="n">
-        <v>668609</v>
+        <v>83495</v>
       </c>
       <c r="I5" t="n">
-        <v>64308</v>
+        <v>161</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7367449</v>
+        <v>1015139</v>
       </c>
       <c r="L5" t="n">
-        <v>10897471</v>
+        <v>1639461</v>
       </c>
       <c r="M5" t="n">
-        <v>4448517</v>
+        <v>642827</v>
       </c>
       <c r="N5" t="n">
-        <v>700154</v>
+        <v>83523</v>
       </c>
       <c r="O5" t="n">
-        <v>2162405</v>
+        <v>327826</v>
       </c>
       <c r="P5" t="n">
-        <v>846720</v>
+        <v>193484</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999945163726807</v>
+        <v>0.9999980330467224</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9065240621566772</v>
+        <v>0.8446040153503418</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8803125619888306</v>
+        <v>0.8085830807685852</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9568938016891479</v>
+        <v>0.933695912361145</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9910053014755249</v>
+        <v>0.986323356628418</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9790211319923401</v>
+        <v>0.9631999731063843</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9935993552207947</v>
+        <v>0.9881740212440491</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>89118</v>
+        <v>8164</v>
       </c>
       <c r="Z5" t="n">
-        <v>946597</v>
+        <v>87570</v>
       </c>
       <c r="AA5" t="n">
-        <v>8835934</v>
+        <v>808667</v>
       </c>
       <c r="AB5" t="n">
-        <v>109931</v>
+        <v>10048</v>
       </c>
       <c r="AC5" t="n">
-        <v>321315</v>
+        <v>29301</v>
       </c>
       <c r="AD5" t="n">
-        <v>6963</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2355496</v>
+        <v>212745</v>
       </c>
       <c r="AG5" t="n">
-        <v>3274384</v>
+        <v>302744</v>
       </c>
       <c r="AH5" t="n">
-        <v>1473924</v>
+        <v>135716</v>
       </c>
       <c r="AI5" t="n">
-        <v>334164</v>
+        <v>30676</v>
       </c>
       <c r="AJ5" t="n">
-        <v>553878</v>
+        <v>50812</v>
       </c>
       <c r="AK5" t="n">
-        <v>146525</v>
+        <v>13405</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734087586402893</v>
+        <v>0.9732111096382141</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641398787498474</v>
+        <v>0.9638177752494812</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983741283416748</v>
+        <v>0.983578622341156</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963043928146362</v>
+        <v>0.9962705373764038</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938869476318359</v>
+        <v>0.993848443031311</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983808398246765</v>
+        <v>0.9983745813369751</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>120</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>154322</v>
+        <v>22802</v>
       </c>
       <c r="E6" t="n">
-        <v>206577</v>
+        <v>27293</v>
       </c>
       <c r="F6" t="n">
-        <v>236138</v>
+        <v>24570</v>
       </c>
       <c r="G6" t="n">
-        <v>285301</v>
+        <v>6584</v>
       </c>
       <c r="H6" t="n">
-        <v>93187</v>
+        <v>8775</v>
       </c>
       <c r="I6" t="n">
-        <v>9810</v>
+        <v>77</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>71955</v>
+        <v>6631</v>
       </c>
       <c r="Z6" t="n">
-        <v>59191</v>
+        <v>5398</v>
       </c>
       <c r="AA6" t="n">
-        <v>120711</v>
+        <v>11132</v>
       </c>
       <c r="AB6" t="n">
-        <v>651291</v>
+        <v>59431</v>
       </c>
       <c r="AC6" t="n">
-        <v>77015</v>
+        <v>7033</v>
       </c>
       <c r="AD6" t="n">
-        <v>5292</v>
+        <v>482</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>256</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>49600</v>
+        <v>17882</v>
       </c>
       <c r="E7" t="n">
-        <v>442357</v>
+        <v>98555</v>
       </c>
       <c r="F7" t="n">
-        <v>1025395</v>
+        <v>149513</v>
       </c>
       <c r="G7" t="n">
-        <v>427877</v>
+        <v>61640</v>
       </c>
       <c r="H7" t="n">
-        <v>3451754</v>
+        <v>184752</v>
       </c>
       <c r="I7" t="n">
-        <v>216920</v>
+        <v>235</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>247</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8916</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>328269</v>
+        <v>30199</v>
       </c>
       <c r="AB7" t="n">
-        <v>83923</v>
+        <v>7730</v>
       </c>
       <c r="AC7" t="n">
-        <v>5060281</v>
+        <v>461766</v>
       </c>
       <c r="AD7" t="n">
-        <v>132523</v>
+        <v>12065</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>335</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>2831</v>
+        <v>1440</v>
       </c>
       <c r="E8" t="n">
-        <v>43187</v>
+        <v>11911</v>
       </c>
       <c r="F8" t="n">
-        <v>91823</v>
+        <v>22990</v>
       </c>
       <c r="G8" t="n">
-        <v>56566</v>
+        <v>13936</v>
       </c>
       <c r="H8" t="n">
-        <v>651978</v>
+        <v>143204</v>
       </c>
       <c r="I8" t="n">
-        <v>1281825</v>
+        <v>448</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>891</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3647</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2927</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>138752</v>
+        <v>12696</v>
       </c>
       <c r="AD8" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
